--- a/data/Data_Globale_Tahiti.xlsx
+++ b/data/Data_Globale_Tahiti.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felix\Documents\Tahiti_Avian_Soundscape_Test\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9109E77-433F-4594-A67A-8F21686E9ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64DA77FB-7A63-47BF-982B-B441D8B20F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6928,7 +6928,7 @@
         <v>327</v>
       </c>
       <c r="O50" s="34">
-        <f t="shared" si="0"/>
+        <f>(P50/31416)</f>
         <v>0.39698242933537053</v>
       </c>
       <c r="P50">
